--- a/artfynd/A 19883-2025 artfynd.xlsx
+++ b/artfynd/A 19883-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076664</v>
       </c>
       <c r="B2" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076653</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076655</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076640</v>
       </c>
       <c r="B5" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,38 +1095,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127076647</v>
+        <v>127076632</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>82852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1137,7 +1136,7 @@
         <v>463309</v>
       </c>
       <c r="R6" t="n">
-        <v>7148881</v>
+        <v>7148867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,37 +1200,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127076632</v>
+        <v>127076647</v>
       </c>
       <c r="B7" t="n">
-        <v>82792</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>463309</v>
       </c>
       <c r="R7" t="n">
-        <v>7148867</v>
+        <v>7148881</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 19883-2025 artfynd.xlsx
+++ b/artfynd/A 19883-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076664</v>
       </c>
       <c r="B2" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076653</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076655</v>
       </c>
       <c r="B4" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076640</v>
       </c>
       <c r="B5" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127076632</v>
       </c>
       <c r="B6" t="n">
-        <v>82852</v>
+        <v>82855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127076647</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19883-2025 artfynd.xlsx
+++ b/artfynd/A 19883-2025 artfynd.xlsx
@@ -1095,37 +1095,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127076632</v>
+        <v>127076647</v>
       </c>
       <c r="B6" t="n">
-        <v>82855</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1136,7 +1137,7 @@
         <v>463309</v>
       </c>
       <c r="R6" t="n">
-        <v>7148867</v>
+        <v>7148881</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,38 +1201,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127076647</v>
+        <v>127076632</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>82855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>463309</v>
       </c>
       <c r="R7" t="n">
-        <v>7148881</v>
+        <v>7148867</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 19883-2025 artfynd.xlsx
+++ b/artfynd/A 19883-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076664</v>
       </c>
       <c r="B2" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076655</v>
       </c>
       <c r="B4" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1095,38 +1095,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127076647</v>
+        <v>127076632</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>82855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1137,7 +1136,7 @@
         <v>463309</v>
       </c>
       <c r="R6" t="n">
-        <v>7148881</v>
+        <v>7148867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,37 +1200,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127076632</v>
+        <v>127076647</v>
       </c>
       <c r="B7" t="n">
-        <v>82855</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>463309</v>
       </c>
       <c r="R7" t="n">
-        <v>7148867</v>
+        <v>7148881</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 19883-2025 artfynd.xlsx
+++ b/artfynd/A 19883-2025 artfynd.xlsx
@@ -1095,37 +1095,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127076632</v>
+        <v>127076647</v>
       </c>
       <c r="B6" t="n">
-        <v>82855</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1136,7 +1137,7 @@
         <v>463309</v>
       </c>
       <c r="R6" t="n">
-        <v>7148867</v>
+        <v>7148881</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,38 +1201,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127076647</v>
+        <v>127076632</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>82855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>463309</v>
       </c>
       <c r="R7" t="n">
-        <v>7148881</v>
+        <v>7148867</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 19883-2025 artfynd.xlsx
+++ b/artfynd/A 19883-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076664</v>
       </c>
       <c r="B2" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076653</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076655</v>
       </c>
       <c r="B4" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076640</v>
       </c>
       <c r="B5" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,38 +1095,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127076647</v>
+        <v>127076632</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>82859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1137,7 +1136,7 @@
         <v>463309</v>
       </c>
       <c r="R6" t="n">
-        <v>7148881</v>
+        <v>7148867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,37 +1200,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127076632</v>
+        <v>127076647</v>
       </c>
       <c r="B7" t="n">
-        <v>82855</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>463309</v>
       </c>
       <c r="R7" t="n">
-        <v>7148867</v>
+        <v>7148881</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 19883-2025 artfynd.xlsx
+++ b/artfynd/A 19883-2025 artfynd.xlsx
@@ -1203,7 +1203,7 @@
         <v>127076647</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 19883-2025 artfynd.xlsx
+++ b/artfynd/A 19883-2025 artfynd.xlsx
@@ -1095,37 +1095,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127076632</v>
+        <v>127076647</v>
       </c>
       <c r="B6" t="n">
-        <v>82859</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1136,7 +1137,7 @@
         <v>463309</v>
       </c>
       <c r="R6" t="n">
-        <v>7148867</v>
+        <v>7148881</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,38 +1201,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127076647</v>
+        <v>127076632</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>82859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>463309</v>
       </c>
       <c r="R7" t="n">
-        <v>7148881</v>
+        <v>7148867</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 19883-2025 artfynd.xlsx
+++ b/artfynd/A 19883-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076664</v>
       </c>
       <c r="B2" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076653</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076655</v>
       </c>
       <c r="B4" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076640</v>
       </c>
       <c r="B5" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,38 +1095,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127076647</v>
+        <v>127076632</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>82861</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1137,7 +1136,7 @@
         <v>463309</v>
       </c>
       <c r="R6" t="n">
-        <v>7148881</v>
+        <v>7148867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,37 +1200,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127076632</v>
+        <v>127076647</v>
       </c>
       <c r="B7" t="n">
-        <v>82859</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>463309</v>
       </c>
       <c r="R7" t="n">
-        <v>7148867</v>
+        <v>7148881</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 19883-2025 artfynd.xlsx
+++ b/artfynd/A 19883-2025 artfynd.xlsx
@@ -1095,37 +1095,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127076632</v>
+        <v>127076647</v>
       </c>
       <c r="B6" t="n">
-        <v>82861</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1136,7 +1137,7 @@
         <v>463309</v>
       </c>
       <c r="R6" t="n">
-        <v>7148867</v>
+        <v>7148881</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,38 +1201,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127076647</v>
+        <v>127076632</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>82861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>463309</v>
       </c>
       <c r="R7" t="n">
-        <v>7148881</v>
+        <v>7148867</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 19883-2025 artfynd.xlsx
+++ b/artfynd/A 19883-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076664</v>
       </c>
       <c r="B2" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076655</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127076647</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 19883-2025 artfynd.xlsx
+++ b/artfynd/A 19883-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076664</v>
       </c>
       <c r="B2" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076653</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076655</v>
       </c>
       <c r="B4" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076640</v>
       </c>
       <c r="B5" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127076647</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>127076632</v>
       </c>
       <c r="B7" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
